--- a/Team-Data/2014-15/1-6-2014-15.xlsx
+++ b/Team-Data/2014-15/1-6-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>3</v>
@@ -751,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>15</v>
@@ -760,7 +827,7 @@
         <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -787,7 +854,7 @@
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>3</v>
@@ -799,7 +866,7 @@
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
@@ -969,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE4" t="n">
         <v>17</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>16</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>17</v>
@@ -1118,7 +1185,7 @@
         <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ4" t="n">
         <v>24</v>
@@ -1127,7 +1194,7 @@
         <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM4" t="n">
         <v>16</v>
@@ -1139,7 +1206,7 @@
         <v>23</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ4" t="n">
         <v>18</v>
@@ -1154,10 +1221,10 @@
         <v>19</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
         <v>20</v>
@@ -1169,7 +1236,7 @@
         <v>14</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1358,7 @@
         <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
         <v>25</v>
@@ -1303,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
@@ -1318,10 +1385,10 @@
         <v>29</v>
       </c>
       <c r="AO5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP5" t="n">
         <v>18</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>19</v>
       </c>
       <c r="AQ5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1540,7 @@
         <v>5</v>
       </c>
       <c r="AF6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG6" t="n">
         <v>6</v>
@@ -1512,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
         <v>3</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -1673,22 +1740,22 @@
         <v>17</v>
       </c>
       <c r="AL7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
         <v>12</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
         <v>4</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
         <v>16</v>
@@ -1697,13 +1764,13 @@
         <v>26</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
         <v>21</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
         <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.743</v>
+        <v>0.722</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
       </c>
       <c r="I8" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="J8" t="n">
-        <v>86.5</v>
+        <v>86.3</v>
       </c>
       <c r="K8" t="n">
         <v>0.477</v>
@@ -1780,7 +1847,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.362</v>
@@ -1789,28 +1856,28 @@
         <v>17.5</v>
       </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.762</v>
+        <v>0.764</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S8" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T8" t="n">
-        <v>42.5</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
         <v>12.2</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X8" t="n">
         <v>5.1</v>
@@ -1822,28 +1889,28 @@
         <v>20.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.7</v>
+        <v>109.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -1861,19 +1928,19 @@
         <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
         <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2092,7 @@
         <v>18</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
@@ -2067,7 +2134,7 @@
         <v>18</v>
       </c>
       <c r="AV9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
         <v>23</v>
@@ -2085,7 +2152,7 @@
         <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC9" t="n">
         <v>19</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -2117,100 +2184,100 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.324</v>
+        <v>0.303</v>
       </c>
       <c r="H10" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J10" t="n">
         <v>85.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L10" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M10" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="O10" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.677</v>
+        <v>0.676</v>
       </c>
       <c r="R10" t="n">
         <v>12.6</v>
       </c>
       <c r="S10" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T10" t="n">
         <v>45.4</v>
       </c>
       <c r="U10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V10" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W10" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y10" t="n">
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="AA10" t="n">
         <v>20</v>
       </c>
       <c r="AB10" t="n">
-        <v>96.8</v>
+        <v>96.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF10" t="n">
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH10" t="n">
         <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ10" t="n">
         <v>8</v>
@@ -2225,10 +2292,10 @@
         <v>9</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP10" t="n">
         <v>17</v>
@@ -2249,10 +2316,10 @@
         <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX10" t="n">
         <v>18</v>
@@ -2261,7 +2328,7 @@
         <v>16</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2480,7 @@
         <v>20</v>
       </c>
       <c r="AP11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ11" t="n">
         <v>7</v>
@@ -2443,10 +2510,10 @@
         <v>5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.676</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J12" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K12" t="n">
         <v>0.432</v>
@@ -2508,19 +2575,19 @@
         <v>11.6</v>
       </c>
       <c r="M12" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="P12" t="n">
-        <v>24.1</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.707</v>
+        <v>0.705</v>
       </c>
       <c r="R12" t="n">
         <v>12.5</v>
@@ -2532,43 +2599,43 @@
         <v>44.2</v>
       </c>
       <c r="U12" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V12" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X12" t="n">
         <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF12" t="n">
         <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH12" t="n">
         <v>9</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2619,16 +2686,16 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>16</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -2765,16 +2832,16 @@
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM13" t="n">
         <v>20</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP13" t="n">
         <v>26</v>
@@ -2792,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -2941,7 +3008,7 @@
         <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2959,13 +3026,13 @@
         <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS14" t="n">
         <v>14</v>
@@ -2977,7 +3044,7 @@
         <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
         <v>13</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="n">
         <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>0.324</v>
+        <v>0.314</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="J15" t="n">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L15" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M15" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O15" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.749</v>
+        <v>0.751</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T15" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="V15" t="n">
         <v>12.4</v>
@@ -3087,37 +3154,37 @@
         <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.4</v>
+        <v>102</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.7</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
@@ -3126,58 +3193,58 @@
         <v>4</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
         <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>4</v>
       </c>
       <c r="AW15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY15" t="n">
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3296,13 +3363,13 @@
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
@@ -3317,7 +3384,7 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO16" t="n">
         <v>9</v>
@@ -3338,7 +3405,7 @@
         <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
         <v>5</v>
@@ -3350,13 +3417,13 @@
         <v>23</v>
       </c>
       <c r="AY16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL17" t="n">
         <v>14</v>
@@ -3499,13 +3566,13 @@
         <v>17</v>
       </c>
       <c r="AN17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>25</v>
@@ -3523,13 +3590,13 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>7</v>
       </c>
       <c r="AX17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3538,10 +3605,10 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
         <v>24</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.514</v>
       </c>
       <c r="H18" t="n">
         <v>48.7</v>
@@ -3591,28 +3658,28 @@
         <v>37.7</v>
       </c>
       <c r="J18" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
         <v>19.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.353</v>
+        <v>0.359</v>
       </c>
       <c r="O18" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P18" t="n">
         <v>21.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.779</v>
+        <v>0.777</v>
       </c>
       <c r="R18" t="n">
         <v>10.3</v>
@@ -3621,10 +3688,10 @@
         <v>30.9</v>
       </c>
       <c r="T18" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U18" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V18" t="n">
         <v>16.9</v>
@@ -3639,55 +3706,55 @@
         <v>4.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI18" t="n">
         <v>14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AM18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ18" t="n">
         <v>6</v>
@@ -3696,13 +3763,13 @@
         <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV18" t="n">
         <v>28</v>
@@ -3726,7 +3793,7 @@
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-10.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3863,7 +3930,7 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>6</v>
@@ -3872,10 +3939,10 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3887,7 +3954,7 @@
         <v>12</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
         <v>4</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -3937,160 +4004,160 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" t="n">
         <v>17</v>
       </c>
       <c r="G20" t="n">
-        <v>0.485</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J20" t="n">
-        <v>84.5</v>
+        <v>85</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.341</v>
+        <v>0.338</v>
       </c>
       <c r="O20" t="n">
         <v>16.9</v>
       </c>
       <c r="P20" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.766</v>
+        <v>0.754</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T20" t="n">
-        <v>42.8</v>
+        <v>43.4</v>
       </c>
       <c r="U20" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
         <v>101.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
       </c>
       <c r="AM20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN20" t="n">
         <v>23</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>21</v>
       </c>
       <c r="AO20" t="n">
         <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT20" t="n">
         <v>11</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>12</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ20" t="n">
         <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4282,7 @@
         <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
         <v>21</v>
@@ -4266,7 +4333,7 @@
         <v>24</v>
       </c>
       <c r="BA21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -4385,13 +4452,13 @@
         <v>15</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>18</v>
@@ -4400,10 +4467,10 @@
         <v>14</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
@@ -4415,7 +4482,7 @@
         <v>10</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ22" t="n">
         <v>21</v>
@@ -4439,16 +4506,16 @@
         <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>12</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -4483,91 +4550,91 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" t="n">
         <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
-        <v>0.361</v>
+        <v>0.351</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J23" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="N23" t="n">
         <v>0.374</v>
       </c>
       <c r="O23" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="P23" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
         <v>19.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>22</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
         <v>22</v>
@@ -4585,13 +4652,13 @@
         <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
       </c>
       <c r="AN23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4600,10 +4667,10 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR23" t="n">
         <v>27</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>28</v>
       </c>
       <c r="AS23" t="n">
         <v>16</v>
@@ -4615,16 +4682,16 @@
         <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>22</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
         <v>17</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-13.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM24" t="n">
         <v>10</v>
@@ -4779,13 +4846,13 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
         <v>25</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY24" t="n">
         <v>25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
         <v>18</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" t="n">
         <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H25" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="J25" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="K25" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L25" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="M25" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="O25" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P25" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="R25" t="n">
         <v>10.6</v>
@@ -4895,13 +4962,13 @@
         <v>31.6</v>
       </c>
       <c r="T25" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U25" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V25" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
         <v>8.4</v>
@@ -4913,22 +4980,22 @@
         <v>3.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA25" t="n">
         <v>21.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>107</v>
+        <v>107.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>12</v>
@@ -4937,7 +5004,7 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
@@ -4946,7 +5013,7 @@
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>4</v>
@@ -4955,13 +5022,13 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
@@ -4970,22 +5037,22 @@
         <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5216,7 @@
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5170,7 +5237,7 @@
         <v>8</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>20</v>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5319,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -5396,13 +5463,13 @@
         <v>35</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="H28" t="n">
         <v>49.3</v>
@@ -5411,49 +5478,49 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.466</v>
+        <v>0.468</v>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.368</v>
+        <v>0.371</v>
       </c>
       <c r="O28" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.756</v>
+        <v>0.761</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
         <v>34.1</v>
       </c>
       <c r="T28" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
         <v>4.4</v>
@@ -5462,19 +5529,19 @@
         <v>19.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.2</v>
+        <v>102.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD28" t="n">
         <v>7</v>
       </c>
       <c r="AE28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF28" t="n">
         <v>11</v>
@@ -5489,13 +5556,13 @@
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>15</v>
@@ -5504,13 +5571,13 @@
         <v>8</v>
       </c>
       <c r="AO28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5525,13 +5592,13 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW28" t="n">
         <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5540,10 +5607,10 @@
         <v>9</v>
       </c>
       <c r="BA28" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>6.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
         <v>7</v>
       </c>
       <c r="AF29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG29" t="n">
         <v>7</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
         <v>5</v>
@@ -5674,7 +5741,7 @@
         <v>9</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5695,7 +5762,7 @@
         <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5704,13 +5771,13 @@
         <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
         <v>25</v>
@@ -5719,7 +5786,7 @@
         <v>22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>19</v>
@@ -5877,19 +5944,19 @@
         <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
         <v>24</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>25</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>8</v>
@@ -6029,13 +6096,13 @@
         <v>8</v>
       </c>
       <c r="AH31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI31" t="n">
         <v>7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK31" t="n">
         <v>4</v>
@@ -6053,7 +6120,7 @@
         <v>24</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>24</v>
@@ -6083,10 +6150,10 @@
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-6-2014-15</t>
+          <t>2015-01-06</t>
         </is>
       </c>
     </row>
